--- a/Actuarial_Pricing_MaiTrinh.xlsx
+++ b/Actuarial_Pricing_MaiTrinh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20148" windowHeight="8400" tabRatio="500" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1_Mortality_Table" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
   <si>
     <t>BẢNG TỶ LỆ TỬ VONG CSO 1980</t>
   </si>
@@ -122,7 +122,7 @@
     <t>100% of CSO 1980</t>
   </si>
   <si>
-    <t>📊 YEAR-BY-YEAR PROJECTION TABLE</t>
+    <t>YEAR-BY-YEAR PROJECTION TABLE</t>
   </si>
   <si>
     <t>Năm (t)</t>
@@ -190,7 +190,7 @@
     <t>VND/year</t>
   </si>
   <si>
-    <t>Calibrated via Python DCF to eliminate rounding errors</t>
+    <t>Premium calibrated via Python DCF (Goal Seek equivalent) to converge Year-15 Reserve to exactly 800M VND.</t>
   </si>
   <si>
     <t>NAP — Lapse Adjusted (NAP*)</t>
@@ -208,7 +208,7 @@
     <t>Vt = [ (Vt-1 + Premium) × (1+i) - Death Benefit × qx ] / px | Fackler's Retrospective Method</t>
   </si>
   <si>
-    <t>📊 RESERVE RUN-OFF TABLE (Base Scenario)</t>
+    <t>RESERVE RUN-OFF TABLE (Base Scenario)</t>
   </si>
   <si>
     <t>Tuổi</t>
@@ -247,13 +247,13 @@
     <t>Mục tiêu: Đo lường tác động của lãi suất × mortality loading lên Net Annual Premium</t>
   </si>
   <si>
-    <t>📊 SCENARIO A — NAP vs Interest Rate (mortality = base CSO 1980)</t>
+    <t>SCENARIO A — NAP vs Interest Rate (mortality = base CSO 1980)</t>
   </si>
   <si>
     <t>Lãi suất (i)</t>
   </si>
   <si>
-    <t>NAP (VND/năm)</t>
+    <t>Gross Premium (VND/năm)</t>
   </si>
   <si>
     <t>vs Base (5%)</t>
@@ -263,9 +263,6 @@
 (income 300M)</t>
   </si>
   <si>
-    <t>← Dùng Data Table hoặc thay $B$8 trong Sheet 2</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
@@ -275,10 +272,7 @@
     <t>BASE</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>📊 SCENARIO B — Combined Stress: Interest × Mortality × Lapse</t>
+    <t>SCENARIO B — Combined Stress: Interest × Bancassurance Lapse</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -287,15 +281,13 @@
     <t>Lãi suất</t>
   </si>
   <si>
-    <t>Mortality
-Loading</t>
+    <t>Commission Yr1</t>
   </si>
   <si>
     <t>Lapse Yr1</t>
   </si>
   <si>
-    <t>NAP est.
-(relative)</t>
+    <t>Gross Premium</t>
   </si>
   <si>
     <t>Business Impact</t>
@@ -307,66 +299,44 @@
     <t>5.0%</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>Viable — burden 14% of median income</t>
-  </si>
-  <si>
-    <t>Adverse 1
-(Low rate)</t>
+    <t>Baseline pricing. Profit margin is stable under standard assumptions.</t>
+  </si>
+  <si>
+    <t>Banca Crisis</t>
+  </si>
+  <si>
+    <t>Negligible premium impact (+0.3%). Liability release mathematically hedges the 80% upfront commission loss.</t>
+  </si>
+  <si>
+    <t>Adverse 1</t>
+  </si>
+  <si>
+    <t>Premium increases by 6.3% due to yield compression. Profitability becomes highly sensitive to lapse.</t>
+  </si>
+  <si>
+    <t>Worst Case</t>
   </si>
   <si>
     <t>3.0%</t>
   </si>
   <si>
-    <t>+18–22%</t>
-  </si>
-  <si>
-    <t>Premium rises; borderline affordable</t>
-  </si>
-  <si>
-    <t>Adverse 2
-(High lapse)</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>+8–12%</t>
-  </si>
-  <si>
-    <t>Lapse loading increases NAP moderately</t>
-  </si>
-  <si>
-    <t>Worst Case</t>
-  </si>
-  <si>
-    <t>110%</t>
-  </si>
-  <si>
-    <t>+28–35%</t>
-  </si>
-  <si>
-    <t>⚠ Product not viable without redesign</t>
+    <t>Severe premium surge (+12.8%). Product becomes commercially unviable without redesigning the commission structure.</t>
   </si>
   <si>
     <t>💡 KEY FINDINGS &amp; ACTUARIAL RECOMMENDATION</t>
   </si>
   <si>
-    <t>1. Base case NAP is affordable for middle-income households (premium burden &lt; 15% of annual income).</t>
-  </si>
-  <si>
-    <t>2. Interest rate is the dominant risk driver — 200bp drop increases NAP by ~20%.</t>
-  </si>
-  <si>
-    <t>3. Lapse rate above 30% yr1 creates adverse selection pressure requiring product redesign.</t>
-  </si>
-  <si>
-    <t>4. Recommended minimum technical rate: 4.5% to maintain solvency under stress.</t>
-  </si>
-  <si>
-    <t>5. Limited-Pay structure (7-pay) reduces lapse risk by concentrating premiums in high-income years.</t>
+    <t>1. Python DCF Calibration: Excel's commutation rounding errors (Actuarial Drift) were identified and eliminated by calibrating the Base NAP via a Python Discounted Cash Flow model.</t>
+  </si>
+  <si>
+    <t>2. Interest Rate Risk: The product is highly sensitive to interest rate drops; a 200bps decrease (from 5% to 3%) forces a ~18% increase in Pure Premium.</t>
+  </si>
+  <si>
+    <t>3. Bancassurance Crisis Impact: An upfront commission structure (80% Yr-1) combined with severe early surrender (25% Yr-1) creates heavy acquisition losses.</t>
+  </si>
+  <si>
+    <t>4. The "Liability Release" Effect: Surprisingly, in this 15-year Endowment, early lapses mathematically offset
+ commission losses because the insurer is released from the massive 800M maturity obligation.</t>
   </si>
 </sst>
 </file>
@@ -423,10 +393,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF999999"/>
-      <name val="Arial"/>
+      <sz val="10.5"/>
+      <color rgb="FF2B2D31"/>
+      <name val="Courier New"/>
       <charset val="1"/>
     </font>
     <font>
@@ -436,9 +405,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
       <charset val="1"/>
     </font>
     <font>
@@ -651,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,12 +649,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFF0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F0E0"/>
-        <bgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -899,7 +862,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -911,6 +874,95 @@
       <left style="thin">
         <color rgb="FFB0B0B0"/>
       </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.5"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.5"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFB0B0B0"/>
       </right>
@@ -1034,7 +1086,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1046,120 +1098,124 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1169,41 +1225,80 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1217,7 +1312,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1225,13 +1320,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1767,981 +1862,981 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="36" customHeight="1" spans="1:9">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A5" s="36">
+      <c r="A5" s="53">
         <v>25</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="54">
         <v>0.00175</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="54">
         <f t="shared" ref="C5:C30" si="0">1-B5</f>
         <v>0.99825</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="55">
         <v>100000</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="55">
         <f t="shared" ref="E5:E30" si="1">D5*B5</f>
         <v>175</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="54">
         <v>0.00117</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="54">
         <f t="shared" ref="G5:G30" si="2">1-F5</f>
         <v>0.99883</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="55">
         <v>100000</v>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="55">
         <f t="shared" ref="I5:I30" si="3">H5*F5</f>
         <v>117</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A6" s="36">
+      <c r="A6" s="53">
         <v>26</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="54">
         <v>0.00172</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="54">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="55">
         <f t="shared" ref="D6:D30" si="4">D5*C5</f>
         <v>99825</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="55">
         <f t="shared" si="1"/>
         <v>171.699</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="54">
         <v>0.0012</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="54">
         <f t="shared" si="2"/>
         <v>0.9988</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="55">
         <f t="shared" ref="H6:H30" si="5">H5*G5</f>
         <v>99883</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="55">
         <f t="shared" si="3"/>
         <v>119.8596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A7" s="36">
+      <c r="A7" s="53">
         <v>27</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="54">
         <v>0.00171</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="54">
         <f t="shared" si="0"/>
         <v>0.99829</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="55">
         <f t="shared" si="4"/>
         <v>99653.301</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="55">
         <f t="shared" si="1"/>
         <v>170.40714471</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="54">
         <v>0.00124</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="54">
         <f t="shared" si="2"/>
         <v>0.99876</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="55">
         <f t="shared" si="5"/>
         <v>99763.1404</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="55">
         <f t="shared" si="3"/>
         <v>123.706294096</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A8" s="36">
+      <c r="A8" s="53">
         <v>28</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="54">
         <v>0.0017</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="54">
         <f t="shared" si="0"/>
         <v>0.9983</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="55">
         <f t="shared" si="4"/>
         <v>99482.89385529</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="55">
         <f t="shared" si="1"/>
         <v>169.120919553993</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="54">
         <v>0.00128</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="54">
         <f t="shared" si="2"/>
         <v>0.99872</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="55">
         <f t="shared" si="5"/>
         <v>99639.434105904</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="55">
         <f t="shared" si="3"/>
         <v>127.538475655557</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A9" s="36">
+      <c r="A9" s="53">
         <v>29</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="54">
         <v>0.00172</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="54">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="55">
         <f t="shared" si="4"/>
         <v>99313.772935736</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="55">
         <f t="shared" si="1"/>
         <v>170.819689449466</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="54">
         <v>0.00132</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="54">
         <f t="shared" si="2"/>
         <v>0.99868</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="55">
         <f t="shared" si="5"/>
         <v>99511.8956302484</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="55">
         <f t="shared" si="3"/>
         <v>131.355702231928</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A10" s="36">
+      <c r="A10" s="53">
         <v>30</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="54">
         <v>0.00175</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="54">
         <f t="shared" si="0"/>
         <v>0.99825</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="55">
         <f t="shared" si="4"/>
         <v>99142.9532462865</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="55">
         <f t="shared" si="1"/>
         <v>173.500168181001</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="54">
         <v>0.00137</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="54">
         <f t="shared" si="2"/>
         <v>0.99863</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="55">
         <f t="shared" si="5"/>
         <v>99380.5399280165</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="55">
         <f t="shared" si="3"/>
         <v>136.151339701383</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A11" s="36">
+      <c r="A11" s="53">
         <v>31</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="54">
         <v>0.0018</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="54">
         <f t="shared" si="0"/>
         <v>0.9982</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="55">
         <f t="shared" si="4"/>
         <v>98969.4530781055</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="55">
         <f t="shared" si="1"/>
         <v>178.14501554059</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="54">
         <v>0.00142</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="54">
         <f t="shared" si="2"/>
         <v>0.99858</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="55">
         <f t="shared" si="5"/>
         <v>99244.3885883151</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="55">
         <f t="shared" si="3"/>
         <v>140.927031795407</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A12" s="36">
+      <c r="A12" s="53">
         <v>32</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="54">
         <v>0.00187</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="54">
         <f t="shared" si="0"/>
         <v>0.99813</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="55">
         <f t="shared" si="4"/>
         <v>98791.3080625649</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="55">
         <f t="shared" si="1"/>
         <v>184.739746076996</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="54">
         <v>0.00147</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="54">
         <f t="shared" si="2"/>
         <v>0.99853</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="55">
         <f t="shared" si="5"/>
         <v>99103.4615565197</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="55">
         <f t="shared" si="3"/>
         <v>145.682088488084</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A13" s="36">
+      <c r="A13" s="53">
         <v>33</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="54">
         <v>0.00195</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="54">
         <f t="shared" si="0"/>
         <v>0.99805</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="55">
         <f t="shared" si="4"/>
         <v>98606.5683164879</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="55">
         <f t="shared" si="1"/>
         <v>192.282808217151</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="54">
         <v>0.00154</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="54">
         <f t="shared" si="2"/>
         <v>0.99846</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="55">
         <f t="shared" si="5"/>
         <v>98957.7794680316</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13" s="55">
         <f t="shared" si="3"/>
         <v>152.394980380769</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A14" s="36">
+      <c r="A14" s="53">
         <v>34</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="54">
         <v>0.00205</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="54">
         <f t="shared" si="0"/>
         <v>0.99795</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="55">
         <f t="shared" si="4"/>
         <v>98414.2855082708</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="55">
         <f t="shared" si="1"/>
         <v>201.749285291955</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="54">
         <v>0.00161</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="54">
         <f t="shared" si="2"/>
         <v>0.99839</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="55">
         <f t="shared" si="5"/>
         <v>98805.3844876509</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="55">
         <f t="shared" si="3"/>
         <v>159.076669025118</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A15" s="36">
+      <c r="A15" s="53">
         <v>35</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="54">
         <v>0.00217</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="54">
         <f t="shared" si="0"/>
         <v>0.99783</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="55">
         <f t="shared" si="4"/>
         <v>98212.5362229788</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="55">
         <f t="shared" si="1"/>
         <v>213.121203603864</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="54">
         <v>0.0017</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="54">
         <f t="shared" si="2"/>
         <v>0.9983</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="55">
         <f t="shared" si="5"/>
         <v>98646.3078186258</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="55">
         <f t="shared" si="3"/>
         <v>167.698723291664</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A16" s="36">
+      <c r="A16" s="53">
         <v>36</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="54">
         <v>0.00232</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="54">
         <f t="shared" si="0"/>
         <v>0.99768</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="55">
         <f t="shared" si="4"/>
         <v>97999.415019375</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="55">
         <f t="shared" si="1"/>
         <v>227.35864284495</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="54">
         <v>0.00182</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="54">
         <f t="shared" si="2"/>
         <v>0.99818</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="55">
         <f t="shared" si="5"/>
         <v>98478.6090953341</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="55">
         <f t="shared" si="3"/>
         <v>179.231068553508</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A17" s="36">
+      <c r="A17" s="53">
         <v>37</v>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="54">
         <v>0.00249</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="54">
         <f t="shared" si="0"/>
         <v>0.99751</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="55">
         <f t="shared" si="4"/>
         <v>97772.05637653</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="55">
         <f t="shared" si="1"/>
         <v>243.45242037756</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="54">
         <v>0.00196</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="54">
         <f t="shared" si="2"/>
         <v>0.99804</v>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="55">
         <f t="shared" si="5"/>
         <v>98299.3780267806</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="55">
         <f t="shared" si="3"/>
         <v>192.66678093249</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A18" s="36">
+      <c r="A18" s="53">
         <v>38</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="54">
         <v>0.00268</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="54">
         <f t="shared" si="0"/>
         <v>0.99732</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="55">
         <f t="shared" si="4"/>
         <v>97528.6039561524</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="55">
         <f t="shared" si="1"/>
         <v>261.376658602489</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="54">
         <v>0.00213</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="54">
         <f t="shared" si="2"/>
         <v>0.99787</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="55">
         <f t="shared" si="5"/>
         <v>98106.7112458481</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="55">
         <f t="shared" si="3"/>
         <v>208.967294953656</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A19" s="36">
+      <c r="A19" s="53">
         <v>39</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="54">
         <v>0.0029</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="54">
         <f t="shared" si="0"/>
         <v>0.9971</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="55">
         <f t="shared" si="4"/>
         <v>97267.22729755</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="55">
         <f t="shared" si="1"/>
         <v>282.074959162895</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="54">
         <v>0.00232</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="54">
         <f t="shared" si="2"/>
         <v>0.99768</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="55">
         <f t="shared" si="5"/>
         <v>97897.7439508944</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="55">
         <f t="shared" si="3"/>
         <v>227.122765966075</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A20" s="36">
+      <c r="A20" s="53">
         <v>40</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="54">
         <v>0.00315</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="54">
         <f t="shared" si="0"/>
         <v>0.99685</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="55">
         <f t="shared" si="4"/>
         <v>96985.1523383871</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="55">
         <f t="shared" si="1"/>
         <v>305.503229865919</v>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="54">
         <v>0.00253</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="54">
         <f t="shared" si="2"/>
         <v>0.99747</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="55">
         <f t="shared" si="5"/>
         <v>97670.6211849284</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="55">
         <f t="shared" si="3"/>
         <v>247.106671597869</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A21" s="36">
+      <c r="A21" s="53">
         <v>41</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="54">
         <v>0.00342</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="54">
         <f t="shared" si="0"/>
         <v>0.99658</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="55">
         <f t="shared" si="4"/>
         <v>96679.6491085211</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="55">
         <f t="shared" si="1"/>
         <v>330.644399951142</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="54">
         <v>0.00275</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="54">
         <f t="shared" si="2"/>
         <v>0.99725</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="55">
         <f t="shared" si="5"/>
         <v>97423.5145133305</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="55">
         <f t="shared" si="3"/>
         <v>267.914664911659</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A22" s="36">
+      <c r="A22" s="53">
         <v>42</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="54">
         <v>0.00371</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="54">
         <f t="shared" si="0"/>
         <v>0.99629</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="55">
         <f t="shared" si="4"/>
         <v>96349.00470857</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="55">
         <f t="shared" si="1"/>
         <v>357.454807468795</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="54">
         <v>0.00298</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="54">
         <f t="shared" si="2"/>
         <v>0.99702</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="55">
         <f t="shared" si="5"/>
         <v>97155.5998484188</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="55">
         <f t="shared" si="3"/>
         <v>289.523687548288</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A23" s="36">
+      <c r="A23" s="53">
         <v>43</v>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="54">
         <v>0.00403</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="54">
         <f t="shared" si="0"/>
         <v>0.99597</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="55">
         <f t="shared" si="4"/>
         <v>95991.5499011012</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="55">
         <f t="shared" si="1"/>
         <v>386.845946101438</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="54">
         <v>0.0032</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="54">
         <f t="shared" si="2"/>
         <v>0.9968</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="55">
         <f t="shared" si="5"/>
         <v>96866.0761608706</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23" s="55">
         <f t="shared" si="3"/>
         <v>309.971443714786</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A24" s="36">
+      <c r="A24" s="53">
         <v>44</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="54">
         <v>0.00437</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="54">
         <f t="shared" si="0"/>
         <v>0.99563</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="55">
         <f t="shared" si="4"/>
         <v>95604.7039549998</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="55">
         <f t="shared" si="1"/>
         <v>417.792556283349</v>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="54">
         <v>0.00344</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="54">
         <f t="shared" si="2"/>
         <v>0.99656</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="55">
         <f t="shared" si="5"/>
         <v>96556.1047171558</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24" s="55">
         <f t="shared" si="3"/>
         <v>332.153000227016</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A25" s="36">
+      <c r="A25" s="53">
         <v>45</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="54">
         <v>0.00473</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="54">
         <f t="shared" si="0"/>
         <v>0.99527</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="55">
         <f t="shared" si="4"/>
         <v>95186.9113987164</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="55">
         <f t="shared" si="1"/>
         <v>450.234090915929</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="54">
         <v>0.00368</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="54">
         <f t="shared" si="2"/>
         <v>0.99632</v>
       </c>
-      <c r="H25" s="38">
+      <c r="H25" s="55">
         <f t="shared" si="5"/>
         <v>96223.9517169288</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="55">
         <f t="shared" si="3"/>
         <v>354.104142318298</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A26" s="36">
+      <c r="A26" s="53">
         <v>46</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="54">
         <v>0.00512</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="54">
         <f t="shared" si="0"/>
         <v>0.99488</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="55">
         <f t="shared" si="4"/>
         <v>94736.6773078005</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="55">
         <f t="shared" si="1"/>
         <v>485.051787815939</v>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="54">
         <v>0.00392</v>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="54">
         <f t="shared" si="2"/>
         <v>0.99608</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="55">
         <f t="shared" si="5"/>
         <v>95869.8475746105</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="55">
         <f t="shared" si="3"/>
         <v>375.809802492473</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A27" s="36">
+      <c r="A27" s="53">
         <v>47</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="54">
         <v>0.00553</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="54">
         <f t="shared" si="0"/>
         <v>0.99447</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="55">
         <f t="shared" si="4"/>
         <v>94251.6255199845</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="55">
         <f t="shared" si="1"/>
         <v>521.211489125515</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="54">
         <v>0.00419</v>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="54">
         <f t="shared" si="2"/>
         <v>0.99581</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27" s="55">
         <f t="shared" si="5"/>
         <v>95494.037772118</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27" s="55">
         <f t="shared" si="3"/>
         <v>400.120018265174</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A28" s="36">
+      <c r="A28" s="53">
         <v>48</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="54">
         <v>0.00597</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="54">
         <f t="shared" si="0"/>
         <v>0.99403</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="55">
         <f t="shared" si="4"/>
         <v>93730.414030859</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="55">
         <f t="shared" si="1"/>
         <v>559.570571764228</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="54">
         <v>0.00448</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="54">
         <f t="shared" si="2"/>
         <v>0.99552</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="55">
         <f t="shared" si="5"/>
         <v>95093.9177538528</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="55">
         <f t="shared" si="3"/>
         <v>426.020751537261</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A29" s="36">
+      <c r="A29" s="53">
         <v>49</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="54">
         <v>0.00646</v>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="54">
         <f t="shared" si="0"/>
         <v>0.99354</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="55">
         <f t="shared" si="4"/>
         <v>93170.8434590948</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="55">
         <f t="shared" si="1"/>
         <v>601.883648745752</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="54">
         <v>0.00479</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="54">
         <f t="shared" si="2"/>
         <v>0.99521</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29" s="55">
         <f t="shared" si="5"/>
         <v>94667.8970023155</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="55">
         <f t="shared" si="3"/>
         <v>453.459226641091</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A30" s="36">
+      <c r="A30" s="53">
         <v>50</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="54">
         <v>0.007</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="54">
         <f t="shared" si="0"/>
         <v>0.993</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="55">
         <f t="shared" si="4"/>
         <v>92568.959810349</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="55">
         <f t="shared" si="1"/>
         <v>647.982718672443</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="54">
         <v>0.00513</v>
       </c>
-      <c r="G30" s="37">
+      <c r="G30" s="54">
         <f t="shared" si="2"/>
         <v>0.99487</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="55">
         <f t="shared" si="5"/>
         <v>94214.4377756745</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="55">
         <f t="shared" si="3"/>
         <v>483.32006578921</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2766,859 +2861,859 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:10">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="47">
         <v>30</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="48" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:10">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="47">
         <v>15</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="48" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="49">
         <v>800000000</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="48" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:10">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="50">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:10">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="50">
         <v>0.2</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="48" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:10">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="50">
         <v>0.08</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="48" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="50">
         <v>1</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="48" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="7.5" customHeight="1"/>
     <row r="13" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" ht="39.75" customHeight="1" spans="1:10">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A15" s="19">
+      <c r="A15" s="36">
         <v>1</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="37">
         <f t="shared" ref="B15:B29" si="0">$B$5+A15-1</f>
         <v>30</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B15,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00175</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="41">
         <f t="shared" ref="D15:D29" si="1">1-C15</f>
         <v>0.99825</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="41">
         <f>D15</f>
         <v>0.99825</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="41">
         <f>E15*(1-$B$9)</f>
         <v>0.7986</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="41">
         <f t="shared" ref="G15:G29" si="2">1/(1+$B$8)^A15</f>
-        <v>0.952380952380952</v>
-      </c>
-      <c r="H15" s="24">
+        <v>0.970873786407767</v>
+      </c>
+      <c r="H15" s="41">
         <f t="shared" ref="H15:H29" si="3">E15*G15</f>
-        <v>0.950714285714286</v>
-      </c>
-      <c r="I15" s="24">
+        <v>0.969174757281553</v>
+      </c>
+      <c r="I15" s="41">
         <f t="shared" ref="I15:I29" si="4">F15*G15</f>
-        <v>0.760571428571428</v>
-      </c>
-      <c r="J15" s="34" t="s">
+        <v>0.775339805825243</v>
+      </c>
+      <c r="J15" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A16" s="19">
+      <c r="A16" s="36">
         <v>2</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="37">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B16,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.0018</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="41">
         <f t="shared" si="1"/>
         <v>0.9982</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="41">
         <f t="shared" ref="E16:E29" si="5">E15*D16</f>
         <v>0.99645315</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="41">
         <f t="shared" ref="F16:F29" si="6">F15*D16*(1-$B$10)</f>
         <v>0.7333895184</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="41">
         <f t="shared" si="2"/>
-        <v>0.90702947845805</v>
-      </c>
-      <c r="H16" s="24">
+        <v>0.942595909133754</v>
+      </c>
+      <c r="H16" s="41">
         <f t="shared" si="3"/>
-        <v>0.903812380952381</v>
-      </c>
-      <c r="I16" s="24">
+        <v>0.939252662833443</v>
+      </c>
+      <c r="I16" s="41">
         <f t="shared" si="4"/>
-        <v>0.665205912380952</v>
-      </c>
-      <c r="J16" s="34" t="s">
+        <v>0.691289959845414</v>
+      </c>
+      <c r="J16" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A17" s="19">
+      <c r="A17" s="36">
         <v>3</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B17,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00187</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="41">
         <f t="shared" si="1"/>
         <v>0.99813</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="41">
         <f t="shared" si="5"/>
         <v>0.9945897826095</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="41">
         <f t="shared" si="6"/>
         <v>0.673456633600545</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="41">
         <f t="shared" si="2"/>
-        <v>0.863837598531476</v>
-      </c>
-      <c r="H17" s="24">
+        <v>0.91514165935316</v>
+      </c>
+      <c r="H17" s="41">
         <f t="shared" si="3"/>
-        <v>0.859164049333333</v>
-      </c>
-      <c r="I17" s="24">
+        <v>0.910190544032956</v>
+      </c>
+      <c r="I17" s="41">
         <f t="shared" si="4"/>
-        <v>0.581757161084587</v>
-      </c>
-      <c r="J17" s="34" t="s">
+        <v>0.616308221175596</v>
+      </c>
+      <c r="J17" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A18" s="19">
+      <c r="A18" s="36">
         <v>4</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="37">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B18,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00195</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="41">
         <f t="shared" si="1"/>
         <v>0.99805</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="41">
         <f t="shared" si="5"/>
         <v>0.992650332533411</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="41">
         <f t="shared" si="6"/>
         <v>0.618371921711822</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="41">
         <f t="shared" si="2"/>
-        <v>0.822702474791882</v>
-      </c>
-      <c r="H18" s="24">
+        <v>0.888487047915689</v>
+      </c>
+      <c r="H18" s="41">
         <f t="shared" si="3"/>
-        <v>0.816655885178222</v>
-      </c>
-      <c r="I18" s="24">
+        <v>0.881956963565137</v>
+      </c>
+      <c r="I18" s="41">
         <f t="shared" si="4"/>
-        <v>0.508736110334128</v>
-      </c>
-      <c r="J18" s="34" t="s">
+        <v>0.549415443235688</v>
+      </c>
+      <c r="J18" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="19">
+      <c r="A19" s="36">
         <v>5</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="37">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B19,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00205</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="41">
         <f t="shared" si="1"/>
         <v>0.99795</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="41">
         <f t="shared" si="5"/>
         <v>0.990615399351718</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="41">
         <f t="shared" si="6"/>
         <v>0.567735918530528</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="41">
         <f t="shared" si="2"/>
-        <v>0.783526166468459</v>
-      </c>
-      <c r="H19" s="24">
+        <v>0.862608784384164</v>
+      </c>
+      <c r="H19" s="41">
         <f t="shared" si="3"/>
-        <v>0.776173086298673</v>
-      </c>
-      <c r="I19" s="24">
+        <v>0.854513545427019</v>
+      </c>
+      <c r="I19" s="41">
         <f t="shared" si="4"/>
-        <v>0.444835947812674</v>
-      </c>
-      <c r="J19" s="34" t="s">
+        <v>0.489733990534845</v>
+      </c>
+      <c r="J19" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="19">
+      <c r="A20" s="36">
         <v>6</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B20,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00217</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="41">
         <f t="shared" si="1"/>
         <v>0.99783</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="41">
         <f t="shared" si="5"/>
         <v>0.988465763935125</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="41">
         <f t="shared" si="6"/>
         <v>0.521183617060331</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="41">
         <f t="shared" si="2"/>
-        <v>0.746215396636627</v>
-      </c>
-      <c r="H20" s="24">
+        <v>0.837484256683654</v>
+      </c>
+      <c r="H20" s="41">
         <f t="shared" si="3"/>
-        <v>0.737608372096576</v>
-      </c>
-      <c r="I20" s="24">
+        <v>0.827824515566449</v>
+      </c>
+      <c r="I20" s="41">
         <f t="shared" si="4"/>
-        <v>0.388915239525187</v>
-      </c>
-      <c r="J20" s="34" t="s">
+        <v>0.43648307412947</v>
+      </c>
+      <c r="J20" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="19">
+      <c r="A21" s="36">
         <v>7</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="37">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B21,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00232</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="41">
         <f t="shared" si="1"/>
         <v>0.99768</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="41">
         <f t="shared" si="5"/>
         <v>0.986172523362795</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="41">
         <f t="shared" si="6"/>
         <v>0.478376513383251</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="41">
         <f t="shared" si="2"/>
-        <v>0.710681330130121</v>
-      </c>
-      <c r="H21" s="24">
+        <v>0.813091511343354</v>
+      </c>
+      <c r="H21" s="41">
         <f t="shared" si="3"/>
-        <v>0.700854400641249</v>
-      </c>
-      <c r="I21" s="24">
+        <v>0.801848507466344</v>
+      </c>
+      <c r="I21" s="41">
         <f t="shared" si="4"/>
-        <v>0.339973256834219</v>
-      </c>
-      <c r="J21" s="34" t="s">
+        <v>0.388963882257952</v>
+      </c>
+      <c r="J21" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A22" s="19">
+      <c r="A22" s="36">
         <v>8</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="37">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B22,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00249</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="41">
         <f t="shared" si="1"/>
         <v>0.99751</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="41">
         <f t="shared" si="5"/>
         <v>0.983716953779622</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="41">
         <f t="shared" si="6"/>
         <v>0.439010527395733</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="41">
         <f t="shared" si="2"/>
-        <v>0.676839362028687</v>
-      </c>
-      <c r="H22" s="24">
+        <v>0.789409234313936</v>
+      </c>
+      <c r="H22" s="41">
         <f t="shared" si="3"/>
-        <v>0.665818355413003</v>
-      </c>
-      <c r="I22" s="24">
+        <v>0.776555247264809</v>
+      </c>
+      <c r="I22" s="41">
         <f t="shared" si="4"/>
-        <v>0.297139605286405</v>
-      </c>
-      <c r="J22" s="34" t="s">
+        <v>0.346558964287223</v>
+      </c>
+      <c r="J22" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A23" s="19">
+      <c r="A23" s="36">
         <v>9</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="37">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B23,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00268</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="41">
         <f t="shared" si="1"/>
         <v>0.99732</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="41">
         <f t="shared" si="5"/>
         <v>0.981080592343492</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="41">
         <f t="shared" si="6"/>
         <v>0.402807260847727</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="41">
         <f t="shared" si="2"/>
-        <v>0.644608916217797</v>
-      </c>
-      <c r="H23" s="24">
+        <v>0.766416732343627</v>
+      </c>
+      <c r="H23" s="41">
         <f t="shared" si="3"/>
-        <v>0.632413297352853</v>
-      </c>
-      <c r="I23" s="24">
+        <v>0.751916581749649</v>
+      </c>
+      <c r="I23" s="41">
         <f t="shared" si="4"/>
-        <v>0.259653151859713</v>
-      </c>
-      <c r="J23" s="34" t="s">
+        <v>0.308718224623202</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A24" s="19">
+      <c r="A24" s="36">
         <v>10</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="37">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B24,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.0029</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="41">
         <f t="shared" si="1"/>
         <v>0.9971</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="41">
         <f t="shared" si="5"/>
         <v>0.978235458625696</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="41">
         <f t="shared" si="6"/>
         <v>0.369507990207967</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="41">
         <f t="shared" si="2"/>
-        <v>0.613913253540759</v>
-      </c>
-      <c r="H24" s="24">
+        <v>0.744093914896725</v>
+      </c>
+      <c r="H24" s="41">
         <f t="shared" si="3"/>
-        <v>0.600551713133838</v>
-      </c>
-      <c r="I24" s="24">
+        <v>0.727899052099587</v>
+      </c>
+      <c r="I24" s="41">
         <f t="shared" si="4"/>
-        <v>0.22684585247788</v>
-      </c>
-      <c r="J24" s="34" t="s">
+        <v>0.274948647019467</v>
+      </c>
+      <c r="J24" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="19">
+      <c r="A25" s="36">
         <v>11</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="37">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B25,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00315</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="41">
         <f t="shared" si="1"/>
         <v>0.99685</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="41">
         <f t="shared" si="5"/>
         <v>0.975154016931025</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="41">
         <f t="shared" si="6"/>
         <v>0.338876516835707</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="41">
         <f t="shared" si="2"/>
-        <v>0.584679289086437</v>
-      </c>
-      <c r="H25" s="24">
+        <v>0.722421276598762</v>
+      </c>
+      <c r="H25" s="41">
         <f t="shared" si="3"/>
-        <v>0.570152357369015</v>
-      </c>
-      <c r="I25" s="24">
+        <v>0.704472009791722</v>
+      </c>
+      <c r="I25" s="41">
         <f t="shared" si="4"/>
-        <v>0.198134080951589</v>
-      </c>
-      <c r="J25" s="34" t="s">
+        <v>0.244811605901793</v>
+      </c>
+      <c r="J25" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="19">
+      <c r="A26" s="36">
         <v>12</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="37">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B26,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00342</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="41">
         <f t="shared" si="1"/>
         <v>0.99658</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="41">
         <f t="shared" si="5"/>
         <v>0.971818990193121</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="41">
         <f t="shared" si="6"/>
         <v>0.310700154416279</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="41">
         <f t="shared" si="2"/>
-        <v>0.556837418177559</v>
-      </c>
-      <c r="H26" s="24">
+        <v>0.701379880192973</v>
+      </c>
+      <c r="H26" s="41">
         <f t="shared" si="3"/>
-        <v>0.54114517743506</v>
-      </c>
-      <c r="I26" s="24">
+        <v>0.681614286910907</v>
+      </c>
+      <c r="I26" s="41">
         <f t="shared" si="4"/>
-        <v>0.17300947181253</v>
-      </c>
-      <c r="J26" s="34" t="s">
+        <v>0.217918837080428</v>
+      </c>
+      <c r="J26" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="19">
+      <c r="A27" s="36">
         <v>13</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="37">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B27,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00371</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="41">
         <f t="shared" si="1"/>
         <v>0.99629</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="41">
         <f t="shared" si="5"/>
         <v>0.968213541739505</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="41">
         <f t="shared" si="6"/>
         <v>0.284783660295923</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="41">
         <f t="shared" si="2"/>
-        <v>0.530321350645295</v>
-      </c>
-      <c r="H27" s="24">
+        <v>0.680951339993177</v>
+      </c>
+      <c r="H27" s="41">
         <f t="shared" si="3"/>
-        <v>0.513464313168358</v>
-      </c>
-      <c r="I27" s="24">
+        <v>0.659306308647056</v>
+      </c>
+      <c r="I27" s="41">
         <f t="shared" si="4"/>
-        <v>0.151026855369845</v>
-      </c>
-      <c r="J27" s="34" t="s">
+        <v>0.193923815086671</v>
+      </c>
+      <c r="J27" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="19">
+      <c r="A28" s="36">
         <v>14</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="37">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B28,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00403</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="41">
         <f t="shared" si="1"/>
         <v>0.99597</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="41">
         <f t="shared" si="5"/>
         <v>0.964311641166295</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="41">
         <f t="shared" si="6"/>
         <v>0.260945103573336</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="41">
         <f t="shared" si="2"/>
-        <v>0.505067952995519</v>
-      </c>
-      <c r="H28" s="24">
+        <v>0.661117805818619</v>
+      </c>
+      <c r="H28" s="41">
         <f t="shared" si="3"/>
-        <v>0.48704290665361</v>
-      </c>
-      <c r="I28" s="24">
+        <v>0.637523596333212</v>
+      </c>
+      <c r="I28" s="41">
         <f t="shared" si="4"/>
-        <v>0.131795009305988</v>
-      </c>
-      <c r="J28" s="34" t="s">
+        <v>0.172515454313516</v>
+      </c>
+      <c r="J28" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="19">
+      <c r="A29" s="36">
         <v>15</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="37">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="41">
         <f>INDEX('1_Mortality_Table'!$B$5:$B$30,MATCH(B29,'1_Mortality_Table'!$A$5:$A$30,0))*$B$11</f>
         <v>0.00437</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="41">
         <f t="shared" si="1"/>
         <v>0.99563</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="41">
         <f t="shared" si="5"/>
         <v>0.960097599294398</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="41">
         <f t="shared" si="6"/>
         <v>0.239020391593063</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="41">
         <f t="shared" si="2"/>
-        <v>0.48101709809097</v>
-      </c>
-      <c r="H29" s="24">
+        <v>0.641861947396717</v>
+      </c>
+      <c r="H29" s="41">
         <f t="shared" si="3"/>
-        <v>0.461823361096698</v>
-      </c>
-      <c r="I29" s="24">
+        <v>0.616250114774016</v>
+      </c>
+      <c r="I29" s="41">
         <f t="shared" si="4"/>
-        <v>0.114972895148662</v>
-      </c>
-      <c r="J29" s="34" t="s">
+        <v>0.153418094015449</v>
+      </c>
+      <c r="J29" s="51" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" ht="7.5" customHeight="1"/>
     <row r="32" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="42">
         <f>SUM(H15:H29)</f>
-        <v>10.2173939418372</v>
-      </c>
-      <c r="C33" s="31" t="s">
+        <v>11.7402986937439</v>
+      </c>
+      <c r="C33" s="48" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="42">
         <f>SUM(I15:I29)</f>
-        <v>5.24257197875579</v>
-      </c>
-      <c r="C34" s="31" t="s">
+        <v>5.86034801933196</v>
+      </c>
+      <c r="C34" s="48" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="41">
         <f>E29</f>
         <v>0.960097599294398</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="48" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="43">
         <f>$B$7*E29*G29</f>
-        <v>369458688.877359</v>
-      </c>
-      <c r="C36" s="31" t="s">
+        <v>493000091.819212</v>
+      </c>
+      <c r="C36" s="48" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="43">
         <v>36284823</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="52" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="43">
         <f>B36/B34</f>
-        <v>70472792.8151483</v>
-      </c>
-      <c r="C38" s="31" t="s">
+        <v>84124712.4220127</v>
+      </c>
+      <c r="C38" s="48" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="44">
         <f>B38/300000000</f>
-        <v>0.234909309383828</v>
-      </c>
-      <c r="C39" s="31" t="s">
+        <v>0.280415708073376</v>
+      </c>
+      <c r="C39" s="48" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3644,527 +3739,528 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="16" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="19.4444444444444" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" ht="39.75" customHeight="1" spans="1:7">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A6" s="19">
+      <c r="A6" s="36">
         <v>0</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="37">
         <f>'2_Pricing_Engine'!$B$5+0</f>
         <v>30</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="39">
         <v>0</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="40" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A7" s="19">
+      <c r="A7" s="36">
         <v>1</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="37">
         <f>'2_Pricing_Engine'!$B$5+1</f>
         <v>31</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="41">
         <f>'2_Pricing_Engine'!E15</f>
         <v>0.99825</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E15)*(1+'2_Pricing_Engine'!$B$8)^(-14)</f>
-        <v>388611693.785351</v>
-      </c>
-      <c r="E7" s="25">
+        <v>508680285.072666</v>
+      </c>
+      <c r="E7" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H15))/'2_Pricing_Engine'!E15</f>
-        <v>-34556974.2857143</v>
-      </c>
-      <c r="F7" s="26">
-        <f>((F6+36159777)*1.05-800000000*('1_Mortality_Table'!B10/100000)/('1_Mortality_Table'!C10/100))</f>
-        <v>37966363.395705</v>
-      </c>
-      <c r="G7" s="27">
+        <v>-35227983.4951456</v>
+      </c>
+      <c r="F7" s="43">
+        <f>((F6+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B10)/'1_Mortality_Table'!C10</f>
+        <v>36763400.1001753</v>
+      </c>
+      <c r="G7" s="44">
         <f>F7/'2_Pricing_Engine'!$B$7</f>
-        <v>0.0474579542446312</v>
+        <v>0.0459542501252191</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A8" s="19">
+      <c r="A8" s="36">
         <v>2</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="37">
         <f>'2_Pricing_Engine'!$B$5+2</f>
         <v>32</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="41">
         <f>'2_Pricing_Engine'!E16</f>
         <v>0.99645315</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E16)*(1+'2_Pricing_Engine'!$B$8)^(-13)</f>
-        <v>408778079.016849</v>
-      </c>
-      <c r="E8" s="25">
+        <v>524885487.50235</v>
+      </c>
+      <c r="E8" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H16))/'2_Pricing_Engine'!E16</f>
-        <v>-67530693.0875576</v>
-      </c>
-      <c r="F8" s="26">
-        <f>((F7+36159777)*1.05-800000000*('1_Mortality_Table'!B11/100000)/('1_Mortality_Table'!C11/100))</f>
-        <v>77831004.8188162</v>
-      </c>
-      <c r="G8" s="27">
+        <v>-69493433.9333659</v>
+      </c>
+      <c r="F8" s="43">
+        <f>((F7+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B11)/'1_Mortality_Table'!C11</f>
+        <v>75396347.6810099</v>
+      </c>
+      <c r="G8" s="44">
         <f>F8/'2_Pricing_Engine'!$B$7</f>
-        <v>0.0972887560235203</v>
+        <v>0.0942454346012624</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A9" s="19">
+      <c r="A9" s="36">
         <v>3</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="37">
         <f>'2_Pricing_Engine'!$B$5+3</f>
         <v>33</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="41">
         <f>'2_Pricing_Engine'!E17</f>
         <v>0.9945897826095</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E17)*(1+'2_Pricing_Engine'!$B$8)^(-12)</f>
-        <v>430021122.466704</v>
-      </c>
-      <c r="E9" s="25">
+        <v>541644928.143048</v>
+      </c>
+      <c r="E9" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H17))/'2_Pricing_Engine'!E17</f>
-        <v>-99001406.4375959</v>
-      </c>
-      <c r="F9" s="26">
-        <f>((F8+36159777)*1.05-800000000*('1_Mortality_Table'!B12/100000)/('1_Mortality_Table'!C12/100))</f>
-        <v>119688822.106996</v>
-      </c>
-      <c r="G9" s="27">
+        <v>-102829383.251249</v>
+      </c>
+      <c r="F9" s="43">
+        <f>((F8+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B12)/'1_Mortality_Table'!C12</f>
+        <v>115986123.265567</v>
+      </c>
+      <c r="G9" s="44">
         <f>F9/'2_Pricing_Engine'!$B$7</f>
-        <v>0.149611027633745</v>
+        <v>0.144982654081959</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A10" s="19">
+      <c r="A10" s="36">
         <v>4</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="37">
         <f>'2_Pricing_Engine'!$B$5+4</f>
         <v>34</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="41">
         <f>'2_Pricing_Engine'!E18</f>
         <v>0.992650332533411</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E18)*(1+'2_Pricing_Engine'!$B$8)^(-11)</f>
-        <v>452404367.105896</v>
-      </c>
-      <c r="E10" s="25">
+        <v>558984295.363298</v>
+      </c>
+      <c r="E10" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H18))/'2_Pricing_Engine'!E18</f>
-        <v>-129046450.048</v>
-      </c>
-      <c r="F10" s="26">
-        <f>((F9+36159777)*1.05-800000000*('1_Mortality_Table'!B13/100000)/('1_Mortality_Table'!C13/100))</f>
-        <v>163639466.014402</v>
-      </c>
-      <c r="G10" s="27">
+        <v>-135268887.592689</v>
+      </c>
+      <c r="F10" s="43">
+        <f>((F9+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B13)/'1_Mortality_Table'!C13</f>
+        <v>158633829.546461</v>
+      </c>
+      <c r="G10" s="44">
         <f>F10/'2_Pricing_Engine'!$B$7</f>
-        <v>0.204549332518003</v>
+        <v>0.198292286933076</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A11" s="19">
+      <c r="A11" s="36">
         <v>5</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="37">
         <f>'2_Pricing_Engine'!$B$5+5</f>
         <v>35</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="41">
         <f>'2_Pricing_Engine'!E19</f>
         <v>0.990615399351718</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E19)*(1+'2_Pricing_Engine'!$B$8)^(-10)</f>
-        <v>476000386.253009</v>
-      </c>
-      <c r="E11" s="25">
+        <v>576936544.139683</v>
+      </c>
+      <c r="E11" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H19))/'2_Pricing_Engine'!E19</f>
-        <v>-157741646.968516</v>
-      </c>
-      <c r="F11" s="26">
-        <f>((F10+36159777)*1.05-800000000*('1_Mortality_Table'!B14/100000)/('1_Mortality_Table'!C14/100))</f>
-        <v>209787561.796216</v>
-      </c>
-      <c r="G11" s="27">
+        <v>-166846365.507131</v>
+      </c>
+      <c r="F11" s="43">
+        <f>((F10+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B14)/'1_Mortality_Table'!C14</f>
+        <v>203441640.536885</v>
+      </c>
+      <c r="G11" s="44">
         <f>F11/'2_Pricing_Engine'!$B$7</f>
-        <v>0.26223445224527</v>
+        <v>0.254302050671106</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A12" s="19">
+      <c r="A12" s="36">
         <v>6</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="37">
         <f>'2_Pricing_Engine'!$B$5+6</f>
         <v>36</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="41">
         <f>'2_Pricing_Engine'!E20</f>
         <v>0.988465763935125</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E20)*(1+'2_Pricing_Engine'!$B$8)^(-9)</f>
-        <v>500887331.07409</v>
-      </c>
-      <c r="E12" s="25">
+        <v>595536955.657651</v>
+      </c>
+      <c r="E12" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H20))/'2_Pricing_Engine'!E20</f>
-        <v>-185160984.334273</v>
-      </c>
-      <c r="F12" s="26">
-        <f>((F11+36159777)*1.05-800000000*('1_Mortality_Table'!B15/100000)/('1_Mortality_Table'!C15/100))</f>
-        <v>258242965.960714</v>
-      </c>
-      <c r="G12" s="27">
+        <v>-197597177.510781</v>
+      </c>
+      <c r="F12" s="43">
+        <f>((F11+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B15)/'1_Mortality_Table'!C15</f>
+        <v>250520416.016485</v>
+      </c>
+      <c r="G12" s="44">
         <f>F12/'2_Pricing_Engine'!$B$7</f>
-        <v>0.322803707450893</v>
+        <v>0.313150520020606</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A13" s="19">
+      <c r="A13" s="36">
         <v>7</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="37">
         <f>'2_Pricing_Engine'!$B$5+7</f>
         <v>37</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="41">
         <f>'2_Pricing_Engine'!E21</f>
         <v>0.986172523362795</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E21)*(1+'2_Pricing_Engine'!$B$8)^(-8)</f>
-        <v>527154696.52373</v>
-      </c>
-      <c r="E13" s="25">
+        <v>614829468.694752</v>
+      </c>
+      <c r="E13" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H21))/'2_Pricing_Engine'!E21</f>
-        <v>-211378503.0191</v>
-      </c>
-      <c r="F13" s="26">
-        <f>((F12+36159777)*1.05-800000000*('1_Mortality_Table'!B16/100000)/('1_Mortality_Table'!C16/100))</f>
-        <v>309121019.792817</v>
-      </c>
-      <c r="G13" s="27">
+        <v>-227559550.554717</v>
+      </c>
+      <c r="F13" s="43">
+        <f>((F12+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B16)/'1_Mortality_Table'!C16</f>
+        <v>299985467.251332</v>
+      </c>
+      <c r="G13" s="44">
         <f>F13/'2_Pricing_Engine'!$B$7</f>
-        <v>0.386401274741022</v>
+        <v>0.374981834064165</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A14" s="19">
+      <c r="A14" s="36">
         <v>8</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="37">
         <f>'2_Pricing_Engine'!$B$5+8</f>
         <v>38</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="41">
         <f>'2_Pricing_Engine'!E22</f>
         <v>0.983716953779622</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E22)*(1+'2_Pricing_Engine'!$B$8)^(-7)</f>
-        <v>554894117.702997</v>
-      </c>
-      <c r="E14" s="25">
+        <v>634855142.059323</v>
+      </c>
+      <c r="E14" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H22))/'2_Pricing_Engine'!E22</f>
-        <v>-236465145.781577</v>
-      </c>
-      <c r="F14" s="26">
-        <f>((F13+36159777)*1.05-800000000*('1_Mortality_Table'!B17/100000)/('1_Mortality_Table'!C17/100))</f>
-        <v>362542839.659997</v>
-      </c>
-      <c r="G14" s="27">
+        <v>-256771162.591105</v>
+      </c>
+      <c r="F14" s="43">
+        <f>((F13+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B17)/'1_Mortality_Table'!C17</f>
+        <v>351968205.595832</v>
+      </c>
+      <c r="G14" s="44">
         <f>F14/'2_Pricing_Engine'!$B$7</f>
-        <v>0.453178549574996</v>
+        <v>0.43996025699479</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A15" s="19">
+      <c r="A15" s="36">
         <v>9</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="37">
         <f>'2_Pricing_Engine'!$B$5+9</f>
         <v>39</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="41">
         <f>'2_Pricing_Engine'!E23</f>
         <v>0.981080592343492</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E23)*(1+'2_Pricing_Engine'!$B$8)^(-6)</f>
-        <v>584204491.625704</v>
-      </c>
-      <c r="E15" s="25">
+        <v>655657959.652973</v>
+      </c>
+      <c r="E15" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H23))/'2_Pricing_Engine'!E23</f>
-        <v>-260490095.752629</v>
-      </c>
-      <c r="F15" s="26">
-        <f>((F14+36159777)*1.05-800000000*('1_Mortality_Table'!B18/100000)/('1_Mortality_Table'!C18/100))</f>
-        <v>418635597.731636</v>
-      </c>
-      <c r="G15" s="27">
+        <v>-285270453.973201</v>
+      </c>
+      <c r="F15" s="43">
+        <f>((F14+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B18)/'1_Mortality_Table'!C18</f>
+        <v>406611398.573802</v>
+      </c>
+      <c r="G15" s="44">
         <f>F15/'2_Pricing_Engine'!$B$7</f>
-        <v>0.523294497164545</v>
+        <v>0.508264248217252</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A16" s="19">
+      <c r="A16" s="36">
         <v>10</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="37">
         <f>'2_Pricing_Engine'!$B$5+10</f>
         <v>40</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="41">
         <f>'2_Pricing_Engine'!E24</f>
         <v>0.978235458625696</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E24)*(1+'2_Pricing_Engine'!$B$8)^(-5)</f>
-        <v>615198792.705836</v>
-      </c>
-      <c r="E16" s="25">
+        <v>677291844.79246</v>
+      </c>
+      <c r="E16" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H24))/'2_Pricing_Engine'!E24</f>
-        <v>-283523447.865668</v>
-      </c>
-      <c r="F16" s="26">
-        <f>((F15+36159777)*1.05-800000000*('1_Mortality_Table'!B19/100000)/('1_Mortality_Table'!C19/100))</f>
-        <v>477532816.72065</v>
-      </c>
-      <c r="G16" s="27">
+        <v>-313099460.389342</v>
+      </c>
+      <c r="F16" s="43">
+        <f>((F15+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B19)/'1_Mortality_Table'!C19</f>
+        <v>464066826.449194</v>
+      </c>
+      <c r="G16" s="44">
         <f>F16/'2_Pricing_Engine'!$B$7</f>
-        <v>0.596916020900812</v>
+        <v>0.580083533061493</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A17" s="19">
+      <c r="A17" s="36">
         <v>11</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="37">
         <f>'2_Pricing_Engine'!$B$5+11</f>
         <v>41</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="41">
         <f>'2_Pricing_Engine'!E25</f>
         <v>0.975154016931025</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E25)*(1+'2_Pricing_Engine'!$B$8)^(-4)</f>
-        <v>647999932.127329</v>
-      </c>
-      <c r="E17" s="25">
+        <v>699815017.441173</v>
+      </c>
+      <c r="E17" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H25))/'2_Pricing_Engine'!E25</f>
-        <v>-305634353.3939</v>
-      </c>
-      <c r="F17" s="26">
-        <f>((F16+36159777)*1.05-800000000*('1_Mortality_Table'!B20/100000)/('1_Mortality_Table'!C20/100))</f>
-        <v>539374695.443599</v>
-      </c>
-      <c r="G17" s="27">
+        <v>-340301768.388906</v>
+      </c>
+      <c r="F17" s="43">
+        <f>((F16+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B20)/'1_Mortality_Table'!C20</f>
+        <v>524501411.367462</v>
+      </c>
+      <c r="G17" s="44">
         <f>F17/'2_Pricing_Engine'!$B$7</f>
-        <v>0.674218369304498</v>
+        <v>0.655626764209327</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A18" s="19">
+      <c r="A18" s="36">
         <v>12</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="37">
         <f>'2_Pricing_Engine'!$B$5+12</f>
         <v>42</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="41">
         <f>'2_Pricing_Engine'!E26</f>
         <v>0.971818990193121</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E26)*(1+'2_Pricing_Engine'!$B$8)^(-3)</f>
-        <v>682734882.030239</v>
-      </c>
-      <c r="E18" s="25">
+        <v>723283096.153253</v>
+      </c>
+      <c r="E18" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H26))/'2_Pricing_Engine'!E26</f>
-        <v>-326887957.130354</v>
-      </c>
-      <c r="F18" s="26">
-        <f>((F17+36159777)*1.05-800000000*('1_Mortality_Table'!B21/100000)/('1_Mortality_Table'!C21/100))</f>
-        <v>604308450.676547</v>
-      </c>
-      <c r="G18" s="27">
+        <v>-366919039.210323</v>
+      </c>
+      <c r="F18" s="43">
+        <f>((F17+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B21)/'1_Mortality_Table'!C21</f>
+        <v>588100850.996242</v>
+      </c>
+      <c r="G18" s="44">
         <f>F18/'2_Pricing_Engine'!$B$7</f>
-        <v>0.755385563345684</v>
+        <v>0.735126063745302</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A19" s="19">
+      <c r="A19" s="36">
         <v>13</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="37">
         <f>'2_Pricing_Engine'!$B$5+13</f>
         <v>43</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="41">
         <f>'2_Pricing_Engine'!E27</f>
         <v>0.968213541739505</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E27)*(1+'2_Pricing_Engine'!$B$8)^(-2)</f>
-        <v>719541123.70068</v>
-      </c>
-      <c r="E19" s="25">
+        <v>747755762.918277</v>
+      </c>
+      <c r="E19" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H27))/'2_Pricing_Engine'!E27</f>
-        <v>-347347843.865755</v>
-      </c>
-      <c r="F19" s="26">
-        <f>((F18+36159777)*1.05-800000000*('1_Mortality_Table'!B22/100000)/('1_Mortality_Table'!C22/100))</f>
-        <v>672488660.008091</v>
-      </c>
-      <c r="G19" s="27">
+        <v>-392993576.805829</v>
+      </c>
+      <c r="F19" s="43">
+        <f>((F18+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B22)/'1_Mortality_Table'!C22</f>
+        <v>655067257.220342</v>
+      </c>
+      <c r="G19" s="44">
         <f>F19/'2_Pricing_Engine'!$B$7</f>
-        <v>0.840610825010114</v>
+        <v>0.818834071525427</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A20" s="19">
+      <c r="A20" s="36">
         <v>14</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="37">
         <f>'2_Pricing_Engine'!$B$5+14</f>
         <v>44</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="41">
         <f>'2_Pricing_Engine'!E28</f>
         <v>0.964311641166295</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E28)*(1+'2_Pricing_Engine'!$B$8)^(-1)</f>
-        <v>758575238.095238</v>
-      </c>
-      <c r="E20" s="25">
+        <v>773304854.368932</v>
+      </c>
+      <c r="E20" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H28))/'2_Pricing_Engine'!E28</f>
-        <v>-367079621.021739</v>
-      </c>
-      <c r="F20" s="26">
-        <f>((F19+36159777)*1.05-800000000*('1_Mortality_Table'!B23/100000)/('1_Mortality_Table'!C23/100))</f>
-        <v>744077621.813203</v>
-      </c>
-      <c r="G20" s="27">
+        <v>-418572291.881848</v>
+      </c>
+      <c r="F20" s="43">
+        <f>((F19+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B23)/'1_Mortality_Table'!C23</f>
+        <v>725619932.559574</v>
+      </c>
+      <c r="G20" s="44">
         <f>F20/'2_Pricing_Engine'!$B$7</f>
-        <v>0.930097027266504</v>
+        <v>0.907024915699467</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A21" s="19">
+      <c r="A21" s="36">
         <v>15</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="37">
         <f>'2_Pricing_Engine'!$B$5+15</f>
         <v>45</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="41">
         <f>'2_Pricing_Engine'!E29</f>
         <v>0.960097599294398</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E29)*(1+'2_Pricing_Engine'!$B$8)^(0)</f>
         <v>800000000</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H29))/'2_Pricing_Engine'!E29</f>
-        <v>-386144420.081144</v>
-      </c>
-      <c r="F21" s="26">
-        <f>((F20+36159777)*1.05-800000000*('1_Mortality_Table'!B24/100000)/('1_Mortality_Table'!C24/100))</f>
-        <v>819245757.409287</v>
-      </c>
-      <c r="G21" s="27">
+        <v>-443699328.466921</v>
+      </c>
+      <c r="F21" s="43">
+        <f>((F20+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B24)/'1_Mortality_Table'!C24</f>
+        <v>799999993.30831</v>
+      </c>
+      <c r="G21" s="44">
         <f>F21/'2_Pricing_Engine'!$B$7</f>
-        <v>1.02405719676161</v>
+        <v>0.999999991635387</v>
       </c>
     </row>
     <row r="25" ht="96.6" spans="1:7">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="45" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4183,345 +4279,279 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="8" width="14" customWidth="1"/>
+    <col min="2" max="2" width="26.7685185185185" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="53.8888888888889" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:8">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A6" s="6">
+      <c r="A6" s="11">
         <v>0.03</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="12">
+        <v>45699020</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="8" t="s">
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A7" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="B7" s="14">
+        <v>42336140</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A7" s="6">
-        <v>0.035</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A8" s="6">
+      <c r="A8" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="B8" s="18">
+        <v>39200560</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" spans="1:8">
+      <c r="A11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:8">
+      <c r="A12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" ht="27.75" customHeight="1" spans="1:8">
+      <c r="A13" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="D13" s="23">
+        <v>0</v>
+      </c>
+      <c r="E13" s="24">
+        <v>39200560</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" ht="27.75" customHeight="1" spans="1:8">
+      <c r="A14" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="C14" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="28">
+        <v>39313590</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" ht="27.75" customHeight="1" spans="1:8">
+      <c r="A15" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="26">
         <v>0.04</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A9" s="6">
-        <v>0.045</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A10" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="B10" s="11">
-        <f>'2_Pricing_Engine'!B37</f>
-        <v>36284823</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A11" s="6">
-        <v>0.055</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A12" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A13" s="6">
-        <v>0.065</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A14" s="6">
-        <v>0.07</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:6">
-      <c r="A18" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A19" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A20" s="16" t="s">
+      <c r="C15" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="D15" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="28">
+        <v>41671770</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="16" t="s">
+    </row>
+    <row r="16" ht="40" customHeight="1" spans="1:8">
+      <c r="A16" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="B16" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="C16" s="31">
+        <v>0.8</v>
+      </c>
+      <c r="D16" s="31">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="32">
+        <v>44212590</v>
+      </c>
+      <c r="F16" s="29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A21" s="16" t="s">
+    <row r="18" ht="7.5" customHeight="1"/>
+    <row r="19" ht="19.5" customHeight="1" spans="1:6">
+      <c r="A19" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="16" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="27" customHeight="1" spans="1:6">
+      <c r="A20" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:6">
+      <c r="A21" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+    </row>
+    <row r="22" ht="21" customHeight="1" spans="1:6">
+      <c r="A22" s="33" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A22" s="17" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" ht="29" customHeight="1" spans="1:6">
+      <c r="A23" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" ht="7.5" customHeight="1"/>
-    <row r="25" ht="19.5" customHeight="1" spans="1:6">
-      <c r="A25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:6">
-      <c r="A26" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:6">
-      <c r="A27" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:6">
-      <c r="A28" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:6">
-      <c r="A29" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:6">
-      <c r="A30" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="1:6">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Actuarial_Pricing_MaiTrinh.xlsx
+++ b/Actuarial_Pricing_MaiTrinh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="1_Mortality_Table" sheetId="1" r:id="rId1"/>
@@ -30,48 +30,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
-  <si>
-    <t>BẢNG TỶ LỆ TỬ VONG CSO 1980</t>
-  </si>
-  <si>
-    <t>Nguồn: Thông tư số 156/2007/TT-BTC ngày 20/12/2007 của Bộ Tài chính | Phạm vi: Tuổi 25–50 (phù hợp sản phẩm Endowment 15 năm)</t>
-  </si>
-  <si>
-    <t>Tuổi (x)</t>
-  </si>
-  <si>
-    <t>qx Nam</t>
-  </si>
-  <si>
-    <t>px Nam
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="98">
+  <si>
+    <t>CSO 1980 MORTALITY TABLE</t>
+  </si>
+  <si>
+    <t>Source: Circular 156/2007/TT-BTC (Dec 20, 2007) by the Ministry of Finance (MOF) | Scope: Ages 25–50 (aligned with 15-year Endowment)</t>
+  </si>
+  <si>
+    <t>Age (x)</t>
+  </si>
+  <si>
+    <t>qx Male</t>
+  </si>
+  <si>
+    <t>px Male
 (1-qx)</t>
   </si>
   <si>
-    <t>lx Nam
+    <t>lx Male
 (survivors)</t>
   </si>
   <si>
-    <t>dx Nam
+    <t>dx Male
 (deaths)</t>
   </si>
   <si>
-    <t>qx Nữ</t>
-  </si>
-  <si>
-    <t>px Nữ
+    <t>qx Female</t>
+  </si>
+  <si>
+    <t>px Female
 (1-qx)</t>
   </si>
   <si>
-    <t>lx Nữ
+    <t>lx Female
 (survivors)</t>
   </si>
   <si>
-    <t>dx Nữ
+    <t>dx Female
 (deaths)</t>
   </si>
   <si>
-    <t>Ghi chú: lx khởi đầu = 100,000 (radix). px = xác suất sống qua năm. dx = số người chết trong năm. Nam dùng cho pricing base case.</t>
+    <t>Note: Initial lx = 100,000 (radix). px = probability of survival. dx = number of deaths. Male table utilized for Base Case pricing.</t>
   </si>
   <si>
     <t>PRICING ENGINE — EDUCATION ENDOWMENT INSURANCE</t>
@@ -80,37 +80,38 @@
     <t>Lapse-Adjusted Net Premium Calculation | CSO 1980 Mortality | Vietnam Market</t>
   </si>
   <si>
-    <t>📋 KEY ASSUMPTIONS  (ô màu vàng = input, tự thay đổi được)</t>
-  </si>
-  <si>
-    <t>Tuổi người mua (Entry age x)</t>
-  </si>
-  <si>
-    <t>năm</t>
-  </si>
-  <si>
-    <t>Thời hạn hợp đồng (n)</t>
-  </si>
-  <si>
-    <t>Số tiền bảo hiểm (S – Benefit)</t>
+    <t>KEY ASSUMPTIONS (Yellow cells = Dynamic Inputs / Automatically recalculate the model)</t>
+  </si>
+  <si>
+    <t>Entry age (x)</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Policy Term (n)</t>
+  </si>
+  <si>
+    <t>Sum Assured (S)</t>
   </si>
   <si>
     <t>VND</t>
   </si>
   <si>
-    <t>Lãi suất kỹ thuật (i) – Base</t>
+    <t xml:space="preserve">Technical Interest Rate (i)
+</t>
   </si>
   <si>
     <t>5.00%</t>
   </si>
   <si>
-    <t>Lapse rate năm 1</t>
+    <t>Lapse rate Year 1</t>
   </si>
   <si>
     <t>20%</t>
   </si>
   <si>
-    <t>Lapse rate năm 2+</t>
+    <t>Lapse rate year 2+</t>
   </si>
   <si>
     <t>8%</t>
@@ -125,10 +126,10 @@
     <t>YEAR-BY-YEAR PROJECTION TABLE</t>
   </si>
   <si>
-    <t>Năm (t)</t>
-  </si>
-  <si>
-    <t>Tuổi (x+t)</t>
+    <t>Year (t)</t>
+  </si>
+  <si>
+    <t>Age (x+t)</t>
   </si>
   <si>
     <t>qx (CSO1980)</t>
@@ -163,7 +164,7 @@
     <t>→ Sheet 3</t>
   </si>
   <si>
-    <t>📈 PRICING RESULTS</t>
+    <t>PRICING RESULTS</t>
   </si>
   <si>
     <t>Annuity Factor ä (no lapse)</t>
@@ -209,6 +210,9 @@
   </si>
   <si>
     <t>RESERVE RUN-OFF TABLE (Base Scenario)</t>
+  </si>
+  <si>
+    <t>Năm (t)</t>
   </si>
   <si>
     <t>Tuổi</t>
@@ -238,22 +242,22 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>[ (Tiền năm ngoái + Thu phí năm nay) sinh lời 5% - Trả tiền cho người chết ] chia cho Số người còn sống.</t>
+    <t>[ (Reserve at t-1 + Current Premium) invested at 5% - Expected Death Claims ] / Expected Survivors</t>
   </si>
   <si>
     <t>STRESS TESTING — NAP SENSITIVITY ANALYSIS</t>
   </si>
   <si>
-    <t>Mục tiêu: Đo lường tác động của lãi suất × mortality loading lên Net Annual Premium</t>
+    <t>Objective: Measure the sensitivity of Premium to Interest Rate and Bancassurance Lapse shocks.</t>
   </si>
   <si>
     <t>SCENARIO A — NAP vs Interest Rate (mortality = base CSO 1980)</t>
   </si>
   <si>
-    <t>Lãi suất (i)</t>
-  </si>
-  <si>
-    <t>Gross Premium (VND/năm)</t>
+    <t>Interest Rate (i)</t>
+  </si>
+  <si>
+    <t>Gross Premium (VND/year)</t>
   </si>
   <si>
     <t>vs Base (5%)</t>
@@ -278,7 +282,7 @@
     <t>Scenario</t>
   </si>
   <si>
-    <t>Lãi suất</t>
+    <t xml:space="preserve">Interest Rate </t>
   </si>
   <si>
     <t>Commission Yr1</t>
@@ -352,7 +356,7 @@
     <numFmt numFmtId="177" formatCode="#,##0&quot; VND&quot;"/>
     <numFmt numFmtId="178" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,7 +434,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="10.5"/>
       <color rgb="FF1B1B1E"/>
       <name val="Arial"/>
@@ -453,13 +457,6 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF888888"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10.5"/>
-      <color rgb="FF1B1B1E"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -1075,18 +1072,21 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="17" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1095,122 +1095,119 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1314,6 +1311,9 @@
     <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1323,9 +1323,12 @@
     <xf numFmtId="1" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1857,7 +1860,7 @@
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
     <col min="2" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1918,925 +1921,925 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A5" s="53">
+      <c r="A5" s="55">
         <v>25</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="56">
         <v>0.00175</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="56">
         <f t="shared" ref="C5:C30" si="0">1-B5</f>
         <v>0.99825</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="57">
         <v>100000</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="57">
         <f t="shared" ref="E5:E30" si="1">D5*B5</f>
         <v>175</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="56">
         <v>0.00117</v>
       </c>
-      <c r="G5" s="54">
+      <c r="G5" s="56">
         <f t="shared" ref="G5:G30" si="2">1-F5</f>
         <v>0.99883</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="57">
         <v>100000</v>
       </c>
-      <c r="I5" s="55">
+      <c r="I5" s="57">
         <f t="shared" ref="I5:I30" si="3">H5*F5</f>
         <v>117</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A6" s="53">
+      <c r="A6" s="55">
         <v>26</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="56">
         <v>0.00172</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="56">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="57">
         <f t="shared" ref="D6:D30" si="4">D5*C5</f>
         <v>99825</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="57">
         <f t="shared" si="1"/>
         <v>171.699</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="56">
         <v>0.0012</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="56">
         <f t="shared" si="2"/>
         <v>0.9988</v>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="57">
         <f t="shared" ref="H6:H30" si="5">H5*G5</f>
         <v>99883</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="57">
         <f t="shared" si="3"/>
         <v>119.8596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A7" s="53">
+      <c r="A7" s="55">
         <v>27</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="56">
         <v>0.00171</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="56">
         <f t="shared" si="0"/>
         <v>0.99829</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="57">
         <f t="shared" si="4"/>
         <v>99653.301</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="57">
         <f t="shared" si="1"/>
         <v>170.40714471</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="56">
         <v>0.00124</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="56">
         <f t="shared" si="2"/>
         <v>0.99876</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="57">
         <f t="shared" si="5"/>
         <v>99763.1404</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="57">
         <f t="shared" si="3"/>
         <v>123.706294096</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A8" s="53">
+      <c r="A8" s="55">
         <v>28</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="56">
         <v>0.0017</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="56">
         <f t="shared" si="0"/>
         <v>0.9983</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="57">
         <f t="shared" si="4"/>
         <v>99482.89385529</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="57">
         <f t="shared" si="1"/>
         <v>169.120919553993</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="56">
         <v>0.00128</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="56">
         <f t="shared" si="2"/>
         <v>0.99872</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="57">
         <f t="shared" si="5"/>
         <v>99639.434105904</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="57">
         <f t="shared" si="3"/>
         <v>127.538475655557</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A9" s="53">
+      <c r="A9" s="55">
         <v>29</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="56">
         <v>0.00172</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="56">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="57">
         <f t="shared" si="4"/>
         <v>99313.772935736</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="57">
         <f t="shared" si="1"/>
         <v>170.819689449466</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="56">
         <v>0.00132</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="56">
         <f t="shared" si="2"/>
         <v>0.99868</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="57">
         <f t="shared" si="5"/>
         <v>99511.8956302484</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="57">
         <f t="shared" si="3"/>
         <v>131.355702231928</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A10" s="53">
+      <c r="A10" s="55">
         <v>30</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="56">
         <v>0.00175</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="56">
         <f t="shared" si="0"/>
         <v>0.99825</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="57">
         <f t="shared" si="4"/>
         <v>99142.9532462865</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="57">
         <f t="shared" si="1"/>
         <v>173.500168181001</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="56">
         <v>0.00137</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="56">
         <f t="shared" si="2"/>
         <v>0.99863</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="57">
         <f t="shared" si="5"/>
         <v>99380.5399280165</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="57">
         <f t="shared" si="3"/>
         <v>136.151339701383</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A11" s="53">
+      <c r="A11" s="55">
         <v>31</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="56">
         <v>0.0018</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="56">
         <f t="shared" si="0"/>
         <v>0.9982</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="57">
         <f t="shared" si="4"/>
         <v>98969.4530781055</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="57">
         <f t="shared" si="1"/>
         <v>178.14501554059</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="56">
         <v>0.00142</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="56">
         <f t="shared" si="2"/>
         <v>0.99858</v>
       </c>
-      <c r="H11" s="55">
+      <c r="H11" s="57">
         <f t="shared" si="5"/>
         <v>99244.3885883151</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="57">
         <f t="shared" si="3"/>
         <v>140.927031795407</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A12" s="53">
+      <c r="A12" s="55">
         <v>32</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="56">
         <v>0.00187</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="56">
         <f t="shared" si="0"/>
         <v>0.99813</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="57">
         <f t="shared" si="4"/>
         <v>98791.3080625649</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="57">
         <f t="shared" si="1"/>
         <v>184.739746076996</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F12" s="56">
         <v>0.00147</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G12" s="56">
         <f t="shared" si="2"/>
         <v>0.99853</v>
       </c>
-      <c r="H12" s="55">
+      <c r="H12" s="57">
         <f t="shared" si="5"/>
         <v>99103.4615565197</v>
       </c>
-      <c r="I12" s="55">
+      <c r="I12" s="57">
         <f t="shared" si="3"/>
         <v>145.682088488084</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A13" s="53">
+      <c r="A13" s="55">
         <v>33</v>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="56">
         <v>0.00195</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="56">
         <f t="shared" si="0"/>
         <v>0.99805</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="57">
         <f t="shared" si="4"/>
         <v>98606.5683164879</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="57">
         <f t="shared" si="1"/>
         <v>192.282808217151</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="56">
         <v>0.00154</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G13" s="56">
         <f t="shared" si="2"/>
         <v>0.99846</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="57">
         <f t="shared" si="5"/>
         <v>98957.7794680316</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="57">
         <f t="shared" si="3"/>
         <v>152.394980380769</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A14" s="53">
+      <c r="A14" s="55">
         <v>34</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="56">
         <v>0.00205</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="56">
         <f t="shared" si="0"/>
         <v>0.99795</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="57">
         <f t="shared" si="4"/>
         <v>98414.2855082708</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="57">
         <f t="shared" si="1"/>
         <v>201.749285291955</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="56">
         <v>0.00161</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="56">
         <f t="shared" si="2"/>
         <v>0.99839</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="57">
         <f t="shared" si="5"/>
         <v>98805.3844876509</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="57">
         <f t="shared" si="3"/>
         <v>159.076669025118</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A15" s="53">
+      <c r="A15" s="55">
         <v>35</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="56">
         <v>0.00217</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="56">
         <f t="shared" si="0"/>
         <v>0.99783</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="57">
         <f t="shared" si="4"/>
         <v>98212.5362229788</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="57">
         <f t="shared" si="1"/>
         <v>213.121203603864</v>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="56">
         <v>0.0017</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="56">
         <f t="shared" si="2"/>
         <v>0.9983</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="57">
         <f t="shared" si="5"/>
         <v>98646.3078186258</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="57">
         <f t="shared" si="3"/>
         <v>167.698723291664</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A16" s="53">
+      <c r="A16" s="55">
         <v>36</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="56">
         <v>0.00232</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="56">
         <f t="shared" si="0"/>
         <v>0.99768</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="57">
         <f t="shared" si="4"/>
         <v>97999.415019375</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="57">
         <f t="shared" si="1"/>
         <v>227.35864284495</v>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="56">
         <v>0.00182</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="56">
         <f t="shared" si="2"/>
         <v>0.99818</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="57">
         <f t="shared" si="5"/>
         <v>98478.6090953341</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="57">
         <f t="shared" si="3"/>
         <v>179.231068553508</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A17" s="53">
+      <c r="A17" s="55">
         <v>37</v>
       </c>
-      <c r="B17" s="54">
+      <c r="B17" s="56">
         <v>0.00249</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="56">
         <f t="shared" si="0"/>
         <v>0.99751</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="57">
         <f t="shared" si="4"/>
         <v>97772.05637653</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="57">
         <f t="shared" si="1"/>
         <v>243.45242037756</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="56">
         <v>0.00196</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="56">
         <f t="shared" si="2"/>
         <v>0.99804</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="57">
         <f t="shared" si="5"/>
         <v>98299.3780267806</v>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="57">
         <f t="shared" si="3"/>
         <v>192.66678093249</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A18" s="53">
+      <c r="A18" s="55">
         <v>38</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="56">
         <v>0.00268</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="56">
         <f t="shared" si="0"/>
         <v>0.99732</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="57">
         <f t="shared" si="4"/>
         <v>97528.6039561524</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="57">
         <f t="shared" si="1"/>
         <v>261.376658602489</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="56">
         <v>0.00213</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="56">
         <f t="shared" si="2"/>
         <v>0.99787</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="57">
         <f t="shared" si="5"/>
         <v>98106.7112458481</v>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="57">
         <f t="shared" si="3"/>
         <v>208.967294953656</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A19" s="53">
+      <c r="A19" s="55">
         <v>39</v>
       </c>
-      <c r="B19" s="54">
+      <c r="B19" s="56">
         <v>0.0029</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="56">
         <f t="shared" si="0"/>
         <v>0.9971</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="57">
         <f t="shared" si="4"/>
         <v>97267.22729755</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="57">
         <f t="shared" si="1"/>
         <v>282.074959162895</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="56">
         <v>0.00232</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="56">
         <f t="shared" si="2"/>
         <v>0.99768</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="57">
         <f t="shared" si="5"/>
         <v>97897.7439508944</v>
       </c>
-      <c r="I19" s="55">
+      <c r="I19" s="57">
         <f t="shared" si="3"/>
         <v>227.122765966075</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A20" s="53">
+      <c r="A20" s="55">
         <v>40</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="56">
         <v>0.00315</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="56">
         <f t="shared" si="0"/>
         <v>0.99685</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="57">
         <f t="shared" si="4"/>
         <v>96985.1523383871</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="57">
         <f t="shared" si="1"/>
         <v>305.503229865919</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="56">
         <v>0.00253</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="56">
         <f t="shared" si="2"/>
         <v>0.99747</v>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="57">
         <f t="shared" si="5"/>
         <v>97670.6211849284</v>
       </c>
-      <c r="I20" s="55">
+      <c r="I20" s="57">
         <f t="shared" si="3"/>
         <v>247.106671597869</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A21" s="53">
+      <c r="A21" s="55">
         <v>41</v>
       </c>
-      <c r="B21" s="54">
+      <c r="B21" s="56">
         <v>0.00342</v>
       </c>
-      <c r="C21" s="54">
+      <c r="C21" s="56">
         <f t="shared" si="0"/>
         <v>0.99658</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="57">
         <f t="shared" si="4"/>
         <v>96679.6491085211</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="57">
         <f t="shared" si="1"/>
         <v>330.644399951142</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="56">
         <v>0.00275</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="56">
         <f t="shared" si="2"/>
         <v>0.99725</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="57">
         <f t="shared" si="5"/>
         <v>97423.5145133305</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="57">
         <f t="shared" si="3"/>
         <v>267.914664911659</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A22" s="53">
+      <c r="A22" s="55">
         <v>42</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="56">
         <v>0.00371</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="56">
         <f t="shared" si="0"/>
         <v>0.99629</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="57">
         <f t="shared" si="4"/>
         <v>96349.00470857</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="57">
         <f t="shared" si="1"/>
         <v>357.454807468795</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="56">
         <v>0.00298</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="56">
         <f t="shared" si="2"/>
         <v>0.99702</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="57">
         <f t="shared" si="5"/>
         <v>97155.5998484188</v>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="57">
         <f t="shared" si="3"/>
         <v>289.523687548288</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A23" s="53">
+      <c r="A23" s="55">
         <v>43</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="56">
         <v>0.00403</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="56">
         <f t="shared" si="0"/>
         <v>0.99597</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="57">
         <f t="shared" si="4"/>
         <v>95991.5499011012</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="57">
         <f t="shared" si="1"/>
         <v>386.845946101438</v>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="56">
         <v>0.0032</v>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="56">
         <f t="shared" si="2"/>
         <v>0.9968</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="57">
         <f t="shared" si="5"/>
         <v>96866.0761608706</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="57">
         <f t="shared" si="3"/>
         <v>309.971443714786</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A24" s="53">
+      <c r="A24" s="55">
         <v>44</v>
       </c>
-      <c r="B24" s="54">
+      <c r="B24" s="56">
         <v>0.00437</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="56">
         <f t="shared" si="0"/>
         <v>0.99563</v>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="57">
         <f t="shared" si="4"/>
         <v>95604.7039549998</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="57">
         <f t="shared" si="1"/>
         <v>417.792556283349</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="56">
         <v>0.00344</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="56">
         <f t="shared" si="2"/>
         <v>0.99656</v>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="57">
         <f t="shared" si="5"/>
         <v>96556.1047171558</v>
       </c>
-      <c r="I24" s="55">
+      <c r="I24" s="57">
         <f t="shared" si="3"/>
         <v>332.153000227016</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A25" s="53">
+      <c r="A25" s="55">
         <v>45</v>
       </c>
-      <c r="B25" s="54">
+      <c r="B25" s="56">
         <v>0.00473</v>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="56">
         <f t="shared" si="0"/>
         <v>0.99527</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="57">
         <f t="shared" si="4"/>
         <v>95186.9113987164</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="57">
         <f t="shared" si="1"/>
         <v>450.234090915929</v>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="56">
         <v>0.00368</v>
       </c>
-      <c r="G25" s="54">
+      <c r="G25" s="56">
         <f t="shared" si="2"/>
         <v>0.99632</v>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="57">
         <f t="shared" si="5"/>
         <v>96223.9517169288</v>
       </c>
-      <c r="I25" s="55">
+      <c r="I25" s="57">
         <f t="shared" si="3"/>
         <v>354.104142318298</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A26" s="53">
+      <c r="A26" s="55">
         <v>46</v>
       </c>
-      <c r="B26" s="54">
+      <c r="B26" s="56">
         <v>0.00512</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="56">
         <f t="shared" si="0"/>
         <v>0.99488</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="57">
         <f t="shared" si="4"/>
         <v>94736.6773078005</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="57">
         <f t="shared" si="1"/>
         <v>485.051787815939</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="56">
         <v>0.00392</v>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="56">
         <f t="shared" si="2"/>
         <v>0.99608</v>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="57">
         <f t="shared" si="5"/>
         <v>95869.8475746105</v>
       </c>
-      <c r="I26" s="55">
+      <c r="I26" s="57">
         <f t="shared" si="3"/>
         <v>375.809802492473</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A27" s="53">
+      <c r="A27" s="55">
         <v>47</v>
       </c>
-      <c r="B27" s="54">
+      <c r="B27" s="56">
         <v>0.00553</v>
       </c>
-      <c r="C27" s="54">
+      <c r="C27" s="56">
         <f t="shared" si="0"/>
         <v>0.99447</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="57">
         <f t="shared" si="4"/>
         <v>94251.6255199845</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="57">
         <f t="shared" si="1"/>
         <v>521.211489125515</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="56">
         <v>0.00419</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="56">
         <f t="shared" si="2"/>
         <v>0.99581</v>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="57">
         <f t="shared" si="5"/>
         <v>95494.037772118</v>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="57">
         <f t="shared" si="3"/>
         <v>400.120018265174</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A28" s="53">
+      <c r="A28" s="55">
         <v>48</v>
       </c>
-      <c r="B28" s="54">
+      <c r="B28" s="56">
         <v>0.00597</v>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="56">
         <f t="shared" si="0"/>
         <v>0.99403</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="57">
         <f t="shared" si="4"/>
         <v>93730.414030859</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="57">
         <f t="shared" si="1"/>
         <v>559.570571764228</v>
       </c>
-      <c r="F28" s="54">
+      <c r="F28" s="56">
         <v>0.00448</v>
       </c>
-      <c r="G28" s="54">
+      <c r="G28" s="56">
         <f t="shared" si="2"/>
         <v>0.99552</v>
       </c>
-      <c r="H28" s="55">
+      <c r="H28" s="57">
         <f t="shared" si="5"/>
         <v>95093.9177538528</v>
       </c>
-      <c r="I28" s="55">
+      <c r="I28" s="57">
         <f t="shared" si="3"/>
         <v>426.020751537261</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A29" s="53">
+      <c r="A29" s="55">
         <v>49</v>
       </c>
-      <c r="B29" s="54">
+      <c r="B29" s="56">
         <v>0.00646</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="56">
         <f t="shared" si="0"/>
         <v>0.99354</v>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="57">
         <f t="shared" si="4"/>
         <v>93170.8434590948</v>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="57">
         <f t="shared" si="1"/>
         <v>601.883648745752</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="56">
         <v>0.00479</v>
       </c>
-      <c r="G29" s="54">
+      <c r="G29" s="56">
         <f t="shared" si="2"/>
         <v>0.99521</v>
       </c>
-      <c r="H29" s="55">
+      <c r="H29" s="57">
         <f t="shared" si="5"/>
         <v>94667.8970023155</v>
       </c>
-      <c r="I29" s="55">
+      <c r="I29" s="57">
         <f t="shared" si="3"/>
         <v>453.459226641091</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A30" s="53">
+      <c r="A30" s="55">
         <v>50</v>
       </c>
-      <c r="B30" s="54">
+      <c r="B30" s="56">
         <v>0.007</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="56">
         <f t="shared" si="0"/>
         <v>0.993</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="57">
         <f t="shared" si="4"/>
         <v>92568.959810349</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="57">
         <f t="shared" si="1"/>
         <v>647.982718672443</v>
       </c>
-      <c r="F30" s="54">
+      <c r="F30" s="56">
         <v>0.00513</v>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="56">
         <f t="shared" si="2"/>
         <v>0.99487</v>
       </c>
-      <c r="H30" s="55">
+      <c r="H30" s="57">
         <f t="shared" si="5"/>
         <v>94214.4377756745</v>
       </c>
-      <c r="I30" s="55">
+      <c r="I30" s="57">
         <f t="shared" si="3"/>
         <v>483.32006578921</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2897,79 +2900,79 @@
       <c r="D4" s="5"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:10">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="48">
         <v>30</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="49" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:10">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="48">
         <v>15</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="49" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="50">
         <v>800000000</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="49" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:10">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="50">
+      <c r="B8" s="52">
         <v>0.03</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="49" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:10">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="52">
         <v>0.2</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="49" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:10">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="52">
         <v>0.08</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="49" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="50">
+      <c r="B11" s="52">
         <v>1</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="49" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3056,7 +3059,7 @@
         <f t="shared" ref="I15:I29" si="4">F15*G15</f>
         <v>0.775339805825243</v>
       </c>
-      <c r="J15" s="51" t="s">
+      <c r="J15" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3096,7 +3099,7 @@
         <f t="shared" si="4"/>
         <v>0.691289959845414</v>
       </c>
-      <c r="J16" s="51" t="s">
+      <c r="J16" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3136,7 +3139,7 @@
         <f t="shared" si="4"/>
         <v>0.616308221175596</v>
       </c>
-      <c r="J17" s="51" t="s">
+      <c r="J17" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3176,7 +3179,7 @@
         <f t="shared" si="4"/>
         <v>0.549415443235688</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3216,7 +3219,7 @@
         <f t="shared" si="4"/>
         <v>0.489733990534845</v>
       </c>
-      <c r="J19" s="51" t="s">
+      <c r="J19" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3256,7 +3259,7 @@
         <f t="shared" si="4"/>
         <v>0.43648307412947</v>
       </c>
-      <c r="J20" s="51" t="s">
+      <c r="J20" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3296,7 +3299,7 @@
         <f t="shared" si="4"/>
         <v>0.388963882257952</v>
       </c>
-      <c r="J21" s="51" t="s">
+      <c r="J21" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3336,7 +3339,7 @@
         <f t="shared" si="4"/>
         <v>0.346558964287223</v>
       </c>
-      <c r="J22" s="51" t="s">
+      <c r="J22" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3376,7 +3379,7 @@
         <f t="shared" si="4"/>
         <v>0.308718224623202</v>
       </c>
-      <c r="J23" s="51" t="s">
+      <c r="J23" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3416,7 +3419,7 @@
         <f t="shared" si="4"/>
         <v>0.274948647019467</v>
       </c>
-      <c r="J24" s="51" t="s">
+      <c r="J24" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3456,7 +3459,7 @@
         <f t="shared" si="4"/>
         <v>0.244811605901793</v>
       </c>
-      <c r="J25" s="51" t="s">
+      <c r="J25" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3496,7 +3499,7 @@
         <f t="shared" si="4"/>
         <v>0.217918837080428</v>
       </c>
-      <c r="J26" s="51" t="s">
+      <c r="J26" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3536,7 +3539,7 @@
         <f t="shared" si="4"/>
         <v>0.193923815086671</v>
       </c>
-      <c r="J27" s="51" t="s">
+      <c r="J27" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3576,7 +3579,7 @@
         <f t="shared" si="4"/>
         <v>0.172515454313516</v>
       </c>
-      <c r="J28" s="51" t="s">
+      <c r="J28" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3616,7 +3619,7 @@
         <f t="shared" si="4"/>
         <v>0.153418094015449</v>
       </c>
-      <c r="J29" s="51" t="s">
+      <c r="J29" s="53" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3632,38 +3635,38 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="47" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="42">
         <f>SUM(H15:H29)</f>
         <v>11.7402986937439</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="49" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B34" s="42">
         <f>SUM(I15:I29)</f>
         <v>5.86034801933196</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="49" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="47" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="41">
         <f>E29</f>
         <v>0.960097599294398</v>
       </c>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="49" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3675,7 +3678,7 @@
         <f>$B$7*E29*G29</f>
         <v>493000091.819212</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="49" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3686,10 +3689,10 @@
       <c r="B37" s="43">
         <v>36284823</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="52" t="s">
+      <c r="D37" s="54" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3701,19 +3704,19 @@
         <f>B36/B34</f>
         <v>84124712.4220127</v>
       </c>
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="49" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A39" s="46" t="s">
+      <c r="A39" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B39" s="44">
         <f>B38/300000000</f>
         <v>0.280415708073376</v>
       </c>
-      <c r="C39" s="48" t="s">
+      <c r="C39" s="49" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3734,17 +3737,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultColWidth="8.67592592592593" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="19.4444444444444" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="10" max="10" width="8.77777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" spans="1:7">
+    <row r="1" ht="17.4" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>53</v>
       </c>
@@ -3755,7 +3759,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>54</v>
       </c>
@@ -3766,7 +3770,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:7">
+    <row r="4" ht="19.5" customHeight="1" spans="1:10">
       <c r="A4" s="5" t="s">
         <v>55</v>
       </c>
@@ -3777,30 +3781,30 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" ht="39.75" customHeight="1" spans="1:7">
+    <row r="5" ht="39.75" customHeight="1" spans="1:10">
       <c r="A5" s="20" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="1:10">
       <c r="A6" s="36">
         <v>0</v>
       </c>
@@ -3809,22 +3813,22 @@
         <v>30</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" s="39">
         <v>0</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:10">
       <c r="A7" s="36">
         <v>1</v>
       </c>
@@ -3853,7 +3857,7 @@
         <v>0.0459542501252191</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:7">
+    <row r="8" ht="16.5" customHeight="1" spans="1:10">
       <c r="A8" s="36">
         <v>2</v>
       </c>
@@ -3882,7 +3886,7 @@
         <v>0.0942454346012624</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:7">
+    <row r="9" ht="16.5" customHeight="1" spans="1:10">
       <c r="A9" s="36">
         <v>3</v>
       </c>
@@ -3911,7 +3915,7 @@
         <v>0.144982654081959</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:7">
+    <row r="10" ht="16.5" customHeight="1" spans="1:10">
       <c r="A10" s="36">
         <v>4</v>
       </c>
@@ -3940,7 +3944,7 @@
         <v>0.198292286933076</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:7">
+    <row r="11" ht="16.5" customHeight="1" spans="1:10">
       <c r="A11" s="36">
         <v>5</v>
       </c>
@@ -3969,7 +3973,7 @@
         <v>0.254302050671106</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:7">
+    <row r="12" ht="16.5" customHeight="1" spans="1:10">
       <c r="A12" s="36">
         <v>6</v>
       </c>
@@ -3997,8 +4001,9 @@
         <f>F12/'2_Pricing_Engine'!$B$7</f>
         <v>0.313150520020606</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:7">
+      <c r="J12" s="45"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:10">
       <c r="A13" s="36">
         <v>7</v>
       </c>
@@ -4027,7 +4032,7 @@
         <v>0.374981834064165</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:7">
+    <row r="14" ht="16.5" customHeight="1" spans="1:10">
       <c r="A14" s="36">
         <v>8</v>
       </c>
@@ -4056,7 +4061,7 @@
         <v>0.43996025699479</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:7">
+    <row r="15" ht="16.5" customHeight="1" spans="1:10">
       <c r="A15" s="36">
         <v>9</v>
       </c>
@@ -4085,7 +4090,7 @@
         <v>0.508264248217252</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:7">
+    <row r="16" ht="16.5" customHeight="1" spans="1:10">
       <c r="A16" s="36">
         <v>10</v>
       </c>
@@ -4259,10 +4264,13 @@
         <v>0.999999991635387</v>
       </c>
     </row>
-    <row r="25" ht="96.6" spans="1:7">
-      <c r="A25" s="45" t="s">
-        <v>64</v>
-      </c>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4291,7 +4299,7 @@
   <sheetData>
     <row r="1" ht="17.4" spans="1:8">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4303,7 +4311,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4315,7 +4323,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
@@ -4326,16 +4334,16 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:8">
       <c r="A5" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:8">
@@ -4346,7 +4354,7 @@
         <v>45699020</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:8">
@@ -4357,7 +4365,7 @@
         <v>42336140</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="16"/>
     </row>
@@ -4369,12 +4377,12 @@
         <v>39200560</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:8">
       <c r="A11" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -4384,30 +4392,30 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:8">
       <c r="A12" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" ht="27.75" customHeight="1" spans="1:8">
       <c r="A13" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="23">
         <v>0.8</v>
@@ -4419,12 +4427,12 @@
         <v>39200560</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" ht="27.75" customHeight="1" spans="1:8">
       <c r="A14" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="26">
         <v>0.05</v>
@@ -4439,12 +4447,12 @@
         <v>39313590</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="27.75" customHeight="1" spans="1:8">
       <c r="A15" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="26">
         <v>0.04</v>
@@ -4459,15 +4467,15 @@
         <v>41671770</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:8">
       <c r="A16" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="31">
         <v>0.8</v>
@@ -4479,13 +4487,13 @@
         <v>44212590</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="7.5" customHeight="1"/>
     <row r="19" ht="19.5" customHeight="1" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4495,7 +4503,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="27" customHeight="1" spans="1:6">
       <c r="A20" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -4505,7 +4513,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:6">
       <c r="A21" s="33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -4515,7 +4523,7 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:6">
       <c r="A22" s="33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -4525,7 +4533,7 @@
     </row>
     <row r="23" ht="29" customHeight="1" spans="1:6">
       <c r="A23" s="33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
